--- a/artfynd/A 27271-2025 artfynd.xlsx
+++ b/artfynd/A 27271-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126651807</v>
       </c>
       <c r="B2" t="n">
-        <v>97231</v>
+        <v>97306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>126650576</v>
       </c>
       <c r="B3" t="n">
-        <v>99112</v>
+        <v>99187</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>126651370</v>
       </c>
       <c r="B6" t="n">
-        <v>97100</v>
+        <v>97175</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27271-2025 artfynd.xlsx
+++ b/artfynd/A 27271-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126651807</v>
       </c>
       <c r="B2" t="n">
-        <v>97306</v>
+        <v>97312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>126650576</v>
       </c>
       <c r="B3" t="n">
-        <v>99187</v>
+        <v>99193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>126651370</v>
       </c>
       <c r="B6" t="n">
-        <v>97175</v>
+        <v>97181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27271-2025 artfynd.xlsx
+++ b/artfynd/A 27271-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126651807</v>
       </c>
       <c r="B2" t="n">
-        <v>97312</v>
+        <v>97313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>126650576</v>
       </c>
       <c r="B3" t="n">
-        <v>99193</v>
+        <v>99194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>126651370</v>
       </c>
       <c r="B6" t="n">
-        <v>97181</v>
+        <v>97182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27271-2025 artfynd.xlsx
+++ b/artfynd/A 27271-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126651807</v>
       </c>
       <c r="B2" t="n">
-        <v>97313</v>
+        <v>97306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>126650576</v>
       </c>
       <c r="B3" t="n">
-        <v>99194</v>
+        <v>99187</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>126651370</v>
       </c>
       <c r="B6" t="n">
-        <v>97182</v>
+        <v>97175</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27271-2025 artfynd.xlsx
+++ b/artfynd/A 27271-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126651807</v>
+        <v>126651370</v>
       </c>
       <c r="B2" t="n">
-        <v>97313</v>
+        <v>97844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224361</v>
+        <v>2617</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Flikbålmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Riccardia multifida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hareslätt, söder om, Vg</t>
+          <t>Hareslätt, sydost om, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>347981</v>
+        <v>348023</v>
       </c>
       <c r="R2" t="n">
-        <v>6430230</v>
+        <v>6430223</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,14 +754,14 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Växte vid ett surdråg.</t>
+          <t>Troligen flikbålsmossa. Växte i ett surdråg med en del nakna ytor. Det var väldigt lite vatten i skogen för tillfället, men här brukar vara blötare.</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
@@ -790,49 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126650576</v>
+        <v>126650828</v>
       </c>
       <c r="B3" t="n">
-        <v>99194</v>
+        <v>92333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222361</v>
+        <v>4217</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hareslätt, söder om, Vg</t>
+          <t>Hareslätt, sydost om, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>347922</v>
+        <v>348098</v>
       </c>
       <c r="R3" t="n">
-        <v>6430231</v>
+        <v>6430216</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,7 +860,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ganska mycket, växte över många kvadratmeter men ihop med annat, inte minst stjärnstarr.</t>
+          <t>Flera fruktkroppar växte på undersidan och sidan om enda 20 cm tjock granlåga som låg över ett surdråg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126650622</v>
+        <v>126650525</v>
       </c>
       <c r="B4" t="n">
-        <v>58514</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208250</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -930,16 +921,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -949,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347984</v>
+        <v>347889</v>
       </c>
       <c r="R4" t="n">
-        <v>6430213</v>
+        <v>6430257</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -989,7 +971,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ca 4 cm lång, rörde sig i ett fuktigt parti av skogen med mycket Sphagnum.</t>
+          <t>Spillkråkehack vid basen av en tallhögstubbe efter födosök.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,7 +980,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1017,32 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126650525</v>
+        <v>126650495</v>
       </c>
       <c r="B5" t="n">
-        <v>57654</v>
+        <v>58815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>208250</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1050,7 +1031,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1060,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>347889</v>
+        <v>347860</v>
       </c>
       <c r="R5" t="n">
-        <v>6430257</v>
+        <v>6430269</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1100,7 +1090,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Spillkråkehack vid basen av en tallhögstubbe efter födosök.</t>
+          <t>Ca 3 cm lång, rörde sig i en ganska fuktig del av skogen, med mycket Spagnum i bottenskiktet.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,6 +1099,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1127,49 +1118,62 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126651370</v>
+        <v>126650622</v>
       </c>
       <c r="B6" t="n">
-        <v>97182</v>
+        <v>58815</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2617</v>
+        <v>208250</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flikbålmossa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Riccardia multifida</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hareslätt, sydost om, Vg</t>
+          <t>Hareslätt, söder om, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>348023</v>
+        <v>347984</v>
       </c>
       <c r="R6" t="n">
-        <v>6430223</v>
+        <v>6430213</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1206,14 +1210,14 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Troligen flikbålsmossa. Växte i ett surdråg med en del nakna ytor. Det var väldigt lite vatten i skogen för tillfället, men här brukar vara blötare.</t>
+          <t>Ca 4 cm lång, rörde sig i ett fuktigt parti av skogen med mycket Sphagnum.</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
@@ -1234,51 +1238,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126650495</v>
+        <v>126650576</v>
       </c>
       <c r="B7" t="n">
-        <v>58514</v>
+        <v>99879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208250</v>
+        <v>222361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1286,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>347860</v>
+        <v>347922</v>
       </c>
       <c r="R7" t="n">
-        <v>6430269</v>
+        <v>6430231</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1326,7 +1317,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ca 3 cm lång, rörde sig i en ganska fuktig del av skogen, med mycket Spagnum i bottenskiktet.</t>
+          <t>Ganska mycket, växte över många kvadratmeter men ihop med annat, inte minst stjärnstarr.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,6 +1342,231 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126650325</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97975</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hareslätt, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>347679</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6430168</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Långared</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126651807</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97975</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hareslätt, söder om, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>347981</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6430230</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Långared</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Växte vid ett surdråg.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27271-2025 artfynd.xlsx
+++ b/artfynd/A 27271-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126651370</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126650828</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126650525</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126650495</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1235,6 +1260,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126650622</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1342,6 +1372,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126650576</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1452,6 +1487,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126650325</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1567,8 +1607,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126651807</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>